--- a/Data/GUP_PER_IA.xlsx
+++ b/Data/GUP_PER_IA.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="in" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A65"/>
+  <dimension ref="A1:A308"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -426,448 +426,2149 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>FI0396,FIAT,Ducato,2002,2006,Diesel,2.8 JTD 8v,94,128,8140.43S,15000123,,,,,</t>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,00000154,,,,,</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>FI0396,FIAT,Ducato,2002,2006,Diesel,2.8 JTD 8v,94,128,8140.43S,15000158,,,,,</t>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,15000123,,,,,</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>FI0396,FIAT,Ducato,2002,2006,Diesel,2.8 JTD 8v,94,128,8140.43S,15000159,,,,,</t>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,15000158,,,,,</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>FI0396,FIAT,Ducato,2002,2006,Diesel,2.8 JTD 8v,94,128,8140.43S,199006282,,,,,</t>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,15000159,,,,,</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>FI0396,FIAT,Ducato,2002,2006,Diesel,2.8 JTD 8v,94,128,8140.43S,199244103,,,,,</t>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199021307,,,,,</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FI0396,FIAT,Ducato,2002,2006,Diesel,2.8 JTD 8v,94,128,8140.43S,199281221,,,,,</t>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199021308,,,,,</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>FI0396,FIAT,Ducato,2002,2006,Diesel,2.8 JTD 8v,94,128,8140.43S,199304719,,,,,</t>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199021622,,,,,</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>FI0396,FIAT,Ducato,2002,2006,Diesel,2.8 JTD 8v,94,128,8140.43S,199309683,,,,,</t>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199021642,,,,,</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>FI0396,FIAT,Ducato,2002,2006,Diesel,2.8 JTD 8v,94,128,8140.43S,199309687,,,,,</t>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199022349,,,,,</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>FI0396,FIAT,Ducato,2002,2006,Diesel,2.8 JTD 8v,94,128,8140.43S,199309703,,,,,</t>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199022381,,,,,</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>FI0396,FIAT,Ducato,2002,2006,Diesel,2.8 JTD 8v,94,128,8140.43S,199309704,,,,,</t>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199022432,,,,,</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>FI0396,FIAT,Ducato,2002,2006,Diesel,2.8 JTD 8v,94,128,8140.43S,199309706,,,,,</t>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199022458,,,,,</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>FI0396,FIAT,Ducato,2002,2006,Diesel,2.8 JTD 8v,94,128,8140.43S,199309711,,,,,</t>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199022536,,,,,</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>FI0396,FIAT,Ducato,2002,2006,Diesel,2.8 JTD 8v,94,128,8140.43S,199309713,,,,,</t>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199022715,,,,,</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>FI0396,FIAT,Ducato,2002,2006,Diesel,2.8 JTD 8v,94,128,8140.43S,199309715,,,,,</t>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199022733,,,,,</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>FI0396,FIAT,Ducato,2002,2006,Diesel,2.8 JTD 8v,94,128,8140.43S,199309720,,,,,</t>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199025702,,,,,</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>FI0396,FIAT,Ducato,2002,2006,Diesel,2.8 JTD 8v,94,128,8140.43S,199309726,,,,,</t>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199027821,,,,,</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>FI0396,FIAT,Ducato,2002,2006,Diesel,2.8 JTD 8v,94,128,8140.43S,199309732,,,,,</t>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199027831,,,,,</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>FI0396,FIAT,Ducato,2002,2006,Diesel,2.8 JTD 8v,94,128,8140.43S,199309738,,,,,</t>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199027848,,,,,</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>FI0396,FIAT,Ducato,2002,2006,Diesel,2.8 JTD 8v,94,128,8140.43S,199309741,,,,,</t>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199055522,,,,,</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>FI0396,FIAT,Ducato,2002,2006,Diesel,2.8 JTD 8v,94,128,8140.43S,199309743,,,,,</t>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199058066,,,,,</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>FI0396,FIAT,Ducato,2002,2006,Diesel,2.8 JTD 8v,94,128,8140.43S,199309787,,,,,</t>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199058514,,,,,</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>FI0396,FIAT,Ducato,2002,2006,Diesel,2.8 JTD 8v,94,128,8140.43S,199309827,,,,,</t>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199058864,,,,,</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>FI0396,FIAT,Ducato,2002,2006,Diesel,2.8 JTD 8v,94,128,8140.43S,199309871,,,,,</t>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199059124,,,,,</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>FI0396,FIAT,Ducato,2002,2006,Diesel,2.8 JTD 8v,94,128,8140.43S,199309894,,,,,</t>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199059371,,,,,</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>FI0396,FIAT,Ducato,2002,2006,Diesel,2.8 JTD 8v,94,128,8140.43S,199309956,,,,,</t>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199059372,,,,,</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>FI0396,FIAT,Ducato,2002,2006,Diesel,2.8 JTD 8v,94,128,8140.43S,199309958,,,,,</t>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199059489,,,,,</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>FI0396,FIAT,Ducato,2002,2006,Diesel,2.8 JTD 8v,94,128,8140.43S,199309964,,,,,</t>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199059492,,,,,</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>FI0396,FIAT,Ducato,2002,2006,Diesel,2.8 JTD 8v,94,128,8140.43S,199309967,,,,,</t>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199059497,,,,,</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>FI0396,FIAT,Ducato,2002,2006,Diesel,2.8 JTD 8v,94,128,8140.43S,199309970,,,,,</t>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199059498,,,,,</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>FI0396,FIAT,Ducato,2002,2006,Diesel,2.8 JTD 8v,94,128,8140.43S,199309974,,,,,</t>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199059499,,,,,</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>FI0396,FIAT,Ducato,2002,2006,Diesel,2.8 JTD 8v,94,128,8140.43S,199309977,,,,,</t>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199059500,,,,,</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>FI0396,FIAT,Ducato,2002,2006,Diesel,2.8 JTD 8v,94,128,8140.43S,199310007,,,,,</t>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199059501,,,,,</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>FI0396,FIAT,Ducato,2002,2006,Diesel,2.8 JTD 8v,94,128,8140.43S,199310118,,,,,</t>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199059502,,,,,</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>FI0396,FIAT,Ducato,2002,2006,Diesel,2.8 JTD 8v,94,128,8140.43S,199310141,,,,,</t>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199059503,,,,,</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>FI0396,FIAT,Ducato,2002,2006,Diesel,2.8 JTD 8v,94,128,8140.43S,199310172,,,,,</t>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199059504,,,,,</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>FI0396,FIAT,Ducato,2002,2006,Diesel,2.8 JTD 8v,94,128,8140.43S,199310185,,,,,</t>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199059505,,,,,</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>FI0396,FIAT,Ducato,2002,2006,Diesel,2.8 JTD 8v,94,128,8140.43S,199310187,,,,,</t>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199059506,,,,,</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>FI0396,FIAT,Ducato,2002,2006,Diesel,2.8 JTD 8v,94,128,8140.43S,199310189,,,,,</t>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199059507,,,,,</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>FI0396,FIAT,Ducato,2002,2006,Diesel,2.8 JTD 8v,94,128,8140.43S,199310191,,,,,</t>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199059508,,,,,</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>FI0396,FIAT,Ducato,2002,2006,Diesel,2.8 JTD 8v,94,128,8140.43S,199310196,,,,,</t>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199059509,,,,,</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>FI0396,FIAT,Ducato,2002,2006,Diesel,2.8 JTD 8v,94,128,8140.43S,199310197,,,,,</t>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199059510,,,,,</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>FI0396,FIAT,Ducato,2002,2006,Diesel,2.8 JTD 8v,94,128,8140.43S,25017263,,,,,</t>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199059511,,,,,</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>FI0396,FIAT,Ducato,2002,2006,Diesel,2.8 JTD 8v,94,128,8140.43S,25019681,,,,,</t>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199059512,,,,,</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>FI0396,FIAT,Ducato,2002,2006,Diesel,2.8 JTD 8v,94,128,8140.43S,25019900,,,,,</t>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199059513,,,,,</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>FI0396,FIAT,Ducato,2002,2006,Diesel,2.8 JTD 8v,94,128,8140.43S,25020941,,,,,</t>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199059514,,,,,</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>FI0396,FIAT,Ducato,2002,2006,Diesel,2.8 JTD 8v,94,128,8140.43S,25031625,,,,,</t>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199059515,,,,,</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>FI0396,FIAT,Ducato,2002,2006,Diesel,2.8 JTD 8v,94,128,8140.43S,25041328,,,,,</t>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199059516,,,,,</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>FI0396,FIAT,Ducato,2002,2006,Diesel,2.8 JTD 8v,94,128,8140.43S,25046820,,,,,</t>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199059517,,,,,</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>FI0396,FIAT,Ducato,2002,2006,Diesel,2.8 JTD 8v,94,128,8140.43S,25046892,,,,,</t>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199059518,,,,,</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>FI0396,FIAT,Ducato,2002,2006,Diesel,2.8 JTD 8v,94,128,8140.43S,25046905,,,,,</t>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199059519,,,,,</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>FI0396,FIAT,Ducato,2002,2006,Diesel,2.8 JTD 8v,94,128,8140.43S,25053805,,,,,</t>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199059520,,,,,</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>FI0396,FIAT,Ducato,2002,2006,Diesel,2.8 JTD 8v,94,128,8140.43S,25059516,,,,,</t>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199059521,,,,,</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>FI0396,FIAT,Ducato,2002,2006,Diesel,2.8 JTD 8v,94,128,8140.43S,50011102,,,,,</t>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199059522,,,,,</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>FI0396,FIAT,Ducato,2002,2006,Diesel,2.8 JTD 8v,94,128,8140.43S,62502266,,,,,</t>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199059523,,,,,</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>FI0396,FIAT,Ducato,2002,2006,Diesel,2.8 JTD 8v,94,128,8140.43S,62502267,,,,,</t>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199059524,,,,,</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>FI0396,FIAT,Ducato,2002,2006,Diesel,2.8 JTD 8v,94,128,8140.43S,62502268,,,,,</t>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199059525,,,,,</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>FI0396,FIAT,Ducato,2002,2006,Diesel,2.8 JTD 8v,94,128,8140.43S,62502269,,,,,</t>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199059526,,,,,</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>FI0396,FIAT,Ducato,2002,2006,Diesel,2.8 JTD 8v,94,128,8140.43S,62502270,,,,,</t>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199059527,,,,,</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>FI0396,FIAT,Ducato,2002,2006,Diesel,2.8 JTD 8v,94,128,8140.43S,62502272,,,,,</t>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199059528,,,,,</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>FI0396,FIAT,Ducato,2002,2006,Diesel,2.8 JTD 8v,94,128,8140.43S,62502329,,,,,</t>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199059529,,,,,</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>FI0396,FIAT,Ducato,2002,2006,Diesel,2.8 JTD 8v,94,128,8140.43S,62503109,,,,,</t>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199059530,,,,,</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>FI0396,FIAT,Ducato,2002,2006,Diesel,2.8 JTD 8v,94,128,8140.43S,62505178,,,,,</t>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199059531,,,,,</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>FI0396,FIAT,Ducato,2002,2006,Diesel,2.8 JTD 8v,94,128,8140.43S,62506917,,,,,</t>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199059532,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199059533,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199059534,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199059535,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199059536,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199065182,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199070760,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199221343,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199225163,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199239738,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199258801,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199263668,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199264025,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199264192,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199264200,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199264204,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199265393,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199265395,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199266129,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199268118,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199275850,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199279619,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199279641,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199279659,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199280337,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199281069,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199281104,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199281138,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199281324,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199281938,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199282044,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199282054,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199282056,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199282069,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199282071,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199282090,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199282107,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199282108,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199282140,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199282141,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199282867,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199283141,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199283144,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199283150,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199283163,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199283200,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199283220,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199283222,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199283239,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199283241,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199283255,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199283302,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199283326,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199283381,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199283418,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199283420,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199283424,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199283426,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199283438,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199283439,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199283441,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199283520,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199283526,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199283576,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199283605,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199283656,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199283741,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199283752,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199283776,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199283808,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199283856,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199283891,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199283996,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199283999,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199284007,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199284010,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199284056,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199284058,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199284061,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199284062,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199284064,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199284071,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199284088,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199284091,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199284096,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199284097,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199284098,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199284104,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199284111,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199284112,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199284113,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199284114,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199284116,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199284118,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199284120,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199284122,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199284124,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199284125,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199284131,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199284132,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199284133,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199284134,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199284135,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199284160,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199284162,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199284171,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199284173,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199284188,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199284191,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199284193,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199284194,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199284206,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199284221,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199284297,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199284298,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199284337,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199284340,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199284477,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199284495,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199284498,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199284503,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199284504,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199285973,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199287413,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199287414,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199287511,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199287534,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199287539,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199287550,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199287556,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199288126,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199288276,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199291340,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199291444,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199291632,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199291650,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199293022,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199293184,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199296765,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199297292,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199297439,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199297442,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199297444,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199297446,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199297461,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199297467,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199302272,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199302328,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199307805,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199307808,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199307812,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199307814,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199307820,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199307823,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199307825,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199308050,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199308056,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199308058,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199308059,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199308064,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199308069,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199308071,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199308080,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199308081,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199308082,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199308085,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199308086,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199308092,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199314140,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199315613,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199316504,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199316575,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199317452,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199317457,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199317469,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199317483,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199317566,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199317569,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,199317577,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,25001938,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,25002717,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,25006239,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,25006518,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,25022743,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,25030423,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,25030538,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,25034451,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,25034452,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,25034453,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,62502122,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,62502124,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,62502548,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,62505768,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,62505988,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,62506007,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,62506008,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,62506009,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,62506130,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,62506136,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,62506137,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,62506138,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,62506140,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,62506141,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,62506142,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,62506146,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,62506149,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,62506150,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,62506153,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,62507592,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,62507667,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,62507668,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,62507691,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,62508088,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,62508238,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,62508239,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,62508241,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,62508242,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,62508243,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,62508244,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,62508245,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,62508247,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,62508248,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,62508249,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,62508250,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,62508251,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,62508253,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,62508254,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,62508255,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,62508256,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,62508257,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,62508265,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,62508266,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,62508267,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,75000016,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,75000017,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,75000021,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,75000025,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,75000029,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,75000464,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,75000517,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,75000518,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,75000520,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,87000003,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>FI2524,FIAT,500,2007,2021,Benzina,1.2 8v,51,70,169 A 4000,122,,,,,</t>
         </is>
       </c>
     </row>

--- a/Data/GUP_PER_IA.xlsx
+++ b/Data/GUP_PER_IA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A308"/>
+  <dimension ref="A1:A483"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2572,6 +2572,1231 @@
         </is>
       </c>
     </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>RE3309,RENAULT,Clio V,2019,9999,Diesel,1.5 Blue dCi 8v,46,63,K9K-872,00000154,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>RE3309,RENAULT,Clio V,2019,9999,Diesel,1.5 Blue dCi 8v,46,63,K9K-872,00001440,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>RE3309,RENAULT,Clio V,2019,9999,Diesel,1.5 Blue dCi 8v,46,63,K9K-872,15000123,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>RE3309,RENAULT,Clio V,2019,9999,Diesel,1.5 Blue dCi 8v,46,63,K9K-872,15000158,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>RE3309,RENAULT,Clio V,2019,9999,Diesel,1.5 Blue dCi 8v,46,63,K9K-872,15000159,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>RE3309,RENAULT,Clio V,2019,9999,Diesel,1.5 Blue dCi 8v,46,63,K9K-872,199090091,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>RE3309,RENAULT,Clio V,2019,9999,Diesel,1.5 Blue dCi 8v,46,63,K9K-872,199090362,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>RE3309,RENAULT,Clio V,2019,9999,Diesel,1.5 Blue dCi 8v,46,63,K9K-872,199090363,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>RE3309,RENAULT,Clio V,2019,9999,Diesel,1.5 Blue dCi 8v,46,63,K9K-872,199204795,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>RE3309,RENAULT,Clio V,2019,9999,Diesel,1.5 Blue dCi 8v,46,63,K9K-872,199204799,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>RE3309,RENAULT,Clio V,2019,9999,Diesel,1.5 Blue dCi 8v,46,63,K9K-872,199204800,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>RE3309,RENAULT,Clio V,2019,9999,Diesel,1.5 Blue dCi 8v,46,63,K9K-872,199224274,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>RE3309,RENAULT,Clio V,2019,9999,Diesel,1.5 Blue dCi 8v,46,63,K9K-872,199242242,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>RE3309,RENAULT,Clio V,2019,9999,Diesel,1.5 Blue dCi 8v,46,63,K9K-872,199242244,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>RE3309,RENAULT,Clio V,2019,9999,Diesel,1.5 Blue dCi 8v,46,63,K9K-872,199242247,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>RE3309,RENAULT,Clio V,2019,9999,Diesel,1.5 Blue dCi 8v,46,63,K9K-872,199242249,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>RE3309,RENAULT,Clio V,2019,9999,Diesel,1.5 Blue dCi 8v,46,63,K9K-872,199250099,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>RE3309,RENAULT,Clio V,2019,9999,Diesel,1.5 Blue dCi 8v,46,63,K9K-872,199263227,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>RE3309,RENAULT,Clio V,2019,9999,Diesel,1.5 Blue dCi 8v,46,63,K9K-872,199273440,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>RE3309,RENAULT,Clio V,2019,9999,Diesel,1.5 Blue dCi 8v,46,63,K9K-872,199273449,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>RE3309,RENAULT,Clio V,2019,9999,Diesel,1.5 Blue dCi 8v,46,63,K9K-872,199273456,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>RE3309,RENAULT,Clio V,2019,9999,Diesel,1.5 Blue dCi 8v,46,63,K9K-872,199273469,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>RE3309,RENAULT,Clio V,2019,9999,Diesel,1.5 Blue dCi 8v,46,63,K9K-872,199273476,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>RE3309,RENAULT,Clio V,2019,9999,Diesel,1.5 Blue dCi 8v,46,63,K9K-872,199273482,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>RE3309,RENAULT,Clio V,2019,9999,Diesel,1.5 Blue dCi 8v,46,63,K9K-872,199273491,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>RE3309,RENAULT,Clio V,2019,9999,Diesel,1.5 Blue dCi 8v,46,63,K9K-872,199273507,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>RE3309,RENAULT,Clio V,2019,9999,Diesel,1.5 Blue dCi 8v,46,63,K9K-872,199273523,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>RE3309,RENAULT,Clio V,2019,9999,Diesel,1.5 Blue dCi 8v,46,63,K9K-872,199273561,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>RE3309,RENAULT,Clio V,2019,9999,Diesel,1.5 Blue dCi 8v,46,63,K9K-872,199273600,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>RE3309,RENAULT,Clio V,2019,9999,Diesel,1.5 Blue dCi 8v,46,63,K9K-872,199273607,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>RE3309,RENAULT,Clio V,2019,9999,Diesel,1.5 Blue dCi 8v,46,63,K9K-872,199273618,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>RE3309,RENAULT,Clio V,2019,9999,Diesel,1.5 Blue dCi 8v,46,63,K9K-872,199273920,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>RE3309,RENAULT,Clio V,2019,9999,Diesel,1.5 Blue dCi 8v,46,63,K9K-872,199273926,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>RE3309,RENAULT,Clio V,2019,9999,Diesel,1.5 Blue dCi 8v,46,63,K9K-872,199273989,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>RE3309,RENAULT,Clio V,2019,9999,Diesel,1.5 Blue dCi 8v,46,63,K9K-872,199274085,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>RE3309,RENAULT,Clio V,2019,9999,Diesel,1.5 Blue dCi 8v,46,63,K9K-872,199274177,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>RE3309,RENAULT,Clio V,2019,9999,Diesel,1.5 Blue dCi 8v,46,63,K9K-872,199274270,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>RE3309,RENAULT,Clio V,2019,9999,Diesel,1.5 Blue dCi 8v,46,63,K9K-872,199274273,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>RE3309,RENAULT,Clio V,2019,9999,Diesel,1.5 Blue dCi 8v,46,63,K9K-872,199274275,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>RE3309,RENAULT,Clio V,2019,9999,Diesel,1.5 Blue dCi 8v,46,63,K9K-872,199274291,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>RE3309,RENAULT,Clio V,2019,9999,Diesel,1.5 Blue dCi 8v,46,63,K9K-872,199274296,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>RE3309,RENAULT,Clio V,2019,9999,Diesel,1.5 Blue dCi 8v,46,63,K9K-872,199274686,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>RE3309,RENAULT,Clio V,2019,9999,Diesel,1.5 Blue dCi 8v,46,63,K9K-872,199276148,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>RE3309,RENAULT,Clio V,2019,9999,Diesel,1.5 Blue dCi 8v,46,63,K9K-872,199294278,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>RE3309,RENAULT,Clio V,2019,9999,Diesel,1.5 Blue dCi 8v,46,63,K9K-872,199303802,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>RE3309,RENAULT,Clio V,2019,9999,Diesel,1.5 Blue dCi 8v,46,63,K9K-872,199309506,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>RE3309,RENAULT,Clio V,2019,9999,Diesel,1.5 Blue dCi 8v,46,63,K9K-872,199314133,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>RE3309,RENAULT,Clio V,2019,9999,Diesel,1.5 Blue dCi 8v,46,63,K9K-872,75004237,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>VW6868,VOLKSWAGEN,Golf VII,2017,2020,Diesel,2.0 TDI 4Motion 16v,81,110,DFGA,00000154,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>VW6868,VOLKSWAGEN,Golf VII,2017,2020,Diesel,2.0 TDI 4Motion 16v,81,110,DFGA,00001440,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>VW6868,VOLKSWAGEN,Golf VII,2017,2020,Diesel,2.0 TDI 4Motion 16v,81,110,DFGA,15000123,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>VW6868,VOLKSWAGEN,Golf VII,2017,2020,Diesel,2.0 TDI 4Motion 16v,81,110,DFGA,15000158,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>VW6868,VOLKSWAGEN,Golf VII,2017,2020,Diesel,2.0 TDI 4Motion 16v,81,110,DFGA,15000159,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>VW6868,VOLKSWAGEN,Golf VII,2017,2020,Diesel,2.0 TDI 4Motion 16v,81,110,DFGA,199001482,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>VW6868,VOLKSWAGEN,Golf VII,2017,2020,Diesel,2.0 TDI 4Motion 16v,81,110,DFGA,199001483,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>VW6868,VOLKSWAGEN,Golf VII,2017,2020,Diesel,2.0 TDI 4Motion 16v,81,110,DFGA,199001484,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>VW6868,VOLKSWAGEN,Golf VII,2017,2020,Diesel,2.0 TDI 4Motion 16v,81,110,DFGA,199001632,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>VW6868,VOLKSWAGEN,Golf VII,2017,2020,Diesel,2.0 TDI 4Motion 16v,81,110,DFGA,199004286,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>VW6868,VOLKSWAGEN,Golf VII,2017,2020,Diesel,2.0 TDI 4Motion 16v,81,110,DFGA,199007077,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>VW6868,VOLKSWAGEN,Golf VII,2017,2020,Diesel,2.0 TDI 4Motion 16v,81,110,DFGA,199053123,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>VW6868,VOLKSWAGEN,Golf VII,2017,2020,Diesel,2.0 TDI 4Motion 16v,81,110,DFGA,199053551,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>VW6868,VOLKSWAGEN,Golf VII,2017,2020,Diesel,2.0 TDI 4Motion 16v,81,110,DFGA,199053556,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>VW6868,VOLKSWAGEN,Golf VII,2017,2020,Diesel,2.0 TDI 4Motion 16v,81,110,DFGA,199053747,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>VW6868,VOLKSWAGEN,Golf VII,2017,2020,Diesel,2.0 TDI 4Motion 16v,81,110,DFGA,199053748,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>VW6868,VOLKSWAGEN,Golf VII,2017,2020,Diesel,2.0 TDI 4Motion 16v,81,110,DFGA,199053749,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>VW6868,VOLKSWAGEN,Golf VII,2017,2020,Diesel,2.0 TDI 4Motion 16v,81,110,DFGA,199053750,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>VW6868,VOLKSWAGEN,Golf VII,2017,2020,Diesel,2.0 TDI 4Motion 16v,81,110,DFGA,199078200,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>VW6868,VOLKSWAGEN,Golf VII,2017,2020,Diesel,2.0 TDI 4Motion 16v,81,110,DFGA,199078201,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>VW6868,VOLKSWAGEN,Golf VII,2017,2020,Diesel,2.0 TDI 4Motion 16v,81,110,DFGA,199094642,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>VW6868,VOLKSWAGEN,Golf VII,2017,2020,Diesel,2.0 TDI 4Motion 16v,81,110,DFGA,199212796,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>VW6868,VOLKSWAGEN,Golf VII,2017,2020,Diesel,2.0 TDI 4Motion 16v,81,110,DFGA,199240473,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>VW6868,VOLKSWAGEN,Golf VII,2017,2020,Diesel,2.0 TDI 4Motion 16v,81,110,DFGA,199253549,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>VW6868,VOLKSWAGEN,Golf VII,2017,2020,Diesel,2.0 TDI 4Motion 16v,81,110,DFGA,199257791,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>VW6868,VOLKSWAGEN,Golf VII,2017,2020,Diesel,2.0 TDI 4Motion 16v,81,110,DFGA,199269064,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>VW6868,VOLKSWAGEN,Golf VII,2017,2020,Diesel,2.0 TDI 4Motion 16v,81,110,DFGA,199269068,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>VW6868,VOLKSWAGEN,Golf VII,2017,2020,Diesel,2.0 TDI 4Motion 16v,81,110,DFGA,199269069,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>VW6868,VOLKSWAGEN,Golf VII,2017,2020,Diesel,2.0 TDI 4Motion 16v,81,110,DFGA,199269073,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>VW6868,VOLKSWAGEN,Golf VII,2017,2020,Diesel,2.0 TDI 4Motion 16v,81,110,DFGA,199269074,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>VW6868,VOLKSWAGEN,Golf VII,2017,2020,Diesel,2.0 TDI 4Motion 16v,81,110,DFGA,199269075,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>VW6868,VOLKSWAGEN,Golf VII,2017,2020,Diesel,2.0 TDI 4Motion 16v,81,110,DFGA,199273748,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>VW6868,VOLKSWAGEN,Golf VII,2017,2020,Diesel,2.0 TDI 4Motion 16v,81,110,DFGA,199273755,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>VW6868,VOLKSWAGEN,Golf VII,2017,2020,Diesel,2.0 TDI 4Motion 16v,81,110,DFGA,199273766,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>VW6868,VOLKSWAGEN,Golf VII,2017,2020,Diesel,2.0 TDI 4Motion 16v,81,110,DFGA,199273767,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>VW6868,VOLKSWAGEN,Golf VII,2017,2020,Diesel,2.0 TDI 4Motion 16v,81,110,DFGA,199273770,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>VW6868,VOLKSWAGEN,Golf VII,2017,2020,Diesel,2.0 TDI 4Motion 16v,81,110,DFGA,199273773,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>VW6868,VOLKSWAGEN,Golf VII,2017,2020,Diesel,2.0 TDI 4Motion 16v,81,110,DFGA,199273776,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>VW6868,VOLKSWAGEN,Golf VII,2017,2020,Diesel,2.0 TDI 4Motion 16v,81,110,DFGA,199273780,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>VW6868,VOLKSWAGEN,Golf VII,2017,2020,Diesel,2.0 TDI 4Motion 16v,81,110,DFGA,199275145,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>VW6868,VOLKSWAGEN,Golf VII,2017,2020,Diesel,2.0 TDI 4Motion 16v,81,110,DFGA,199275970,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>VW6868,VOLKSWAGEN,Golf VII,2017,2020,Diesel,2.0 TDI 4Motion 16v,81,110,DFGA,199275991,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>VW6868,VOLKSWAGEN,Golf VII,2017,2020,Diesel,2.0 TDI 4Motion 16v,81,110,DFGA,199276264,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>VW6868,VOLKSWAGEN,Golf VII,2017,2020,Diesel,2.0 TDI 4Motion 16v,81,110,DFGA,199283103,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>VW6868,VOLKSWAGEN,Golf VII,2017,2020,Diesel,2.0 TDI 4Motion 16v,81,110,DFGA,199283583,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>VW6868,VOLKSWAGEN,Golf VII,2017,2020,Diesel,2.0 TDI 4Motion 16v,81,110,DFGA,199287943,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>VW6868,VOLKSWAGEN,Golf VII,2017,2020,Diesel,2.0 TDI 4Motion 16v,81,110,DFGA,199287945,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>VW6868,VOLKSWAGEN,Golf VII,2017,2020,Diesel,2.0 TDI 4Motion 16v,81,110,DFGA,199287948,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>VW6868,VOLKSWAGEN,Golf VII,2017,2020,Diesel,2.0 TDI 4Motion 16v,81,110,DFGA,199287951,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>VW6868,VOLKSWAGEN,Golf VII,2017,2020,Diesel,2.0 TDI 4Motion 16v,81,110,DFGA,199287993,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>VW6868,VOLKSWAGEN,Golf VII,2017,2020,Diesel,2.0 TDI 4Motion 16v,81,110,DFGA,199287994,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>VW6868,VOLKSWAGEN,Golf VII,2017,2020,Diesel,2.0 TDI 4Motion 16v,81,110,DFGA,199287995,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>VW6868,VOLKSWAGEN,Golf VII,2017,2020,Diesel,2.0 TDI 4Motion 16v,81,110,DFGA,199287997,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>VW6868,VOLKSWAGEN,Golf VII,2017,2020,Diesel,2.0 TDI 4Motion 16v,81,110,DFGA,199288025,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>VW6868,VOLKSWAGEN,Golf VII,2017,2020,Diesel,2.0 TDI 4Motion 16v,81,110,DFGA,199288032,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>VW6868,VOLKSWAGEN,Golf VII,2017,2020,Diesel,2.0 TDI 4Motion 16v,81,110,DFGA,199288172,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>VW6868,VOLKSWAGEN,Golf VII,2017,2020,Diesel,2.0 TDI 4Motion 16v,81,110,DFGA,199288176,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>VW6868,VOLKSWAGEN,Golf VII,2017,2020,Diesel,2.0 TDI 4Motion 16v,81,110,DFGA,199288178,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>VW6868,VOLKSWAGEN,Golf VII,2017,2020,Diesel,2.0 TDI 4Motion 16v,81,110,DFGA,199288548,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>VW6868,VOLKSWAGEN,Golf VII,2017,2020,Diesel,2.0 TDI 4Motion 16v,81,110,DFGA,199290465,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>VW6868,VOLKSWAGEN,Golf VII,2017,2020,Diesel,2.0 TDI 4Motion 16v,81,110,DFGA,199294221,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>VW6868,VOLKSWAGEN,Golf VII,2017,2020,Diesel,2.0 TDI 4Motion 16v,81,110,DFGA,199294264,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>VW6868,VOLKSWAGEN,Golf VII,2017,2020,Diesel,2.0 TDI 4Motion 16v,81,110,DFGA,199297523,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>VW6868,VOLKSWAGEN,Golf VII,2017,2020,Diesel,2.0 TDI 4Motion 16v,81,110,DFGA,199297744,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>VW6868,VOLKSWAGEN,Golf VII,2017,2020,Diesel,2.0 TDI 4Motion 16v,81,110,DFGA,199297749,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>VW6868,VOLKSWAGEN,Golf VII,2017,2020,Diesel,2.0 TDI 4Motion 16v,81,110,DFGA,199297750,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>VW6868,VOLKSWAGEN,Golf VII,2017,2020,Diesel,2.0 TDI 4Motion 16v,81,110,DFGA,199298110,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>VW6868,VOLKSWAGEN,Golf VII,2017,2020,Diesel,2.0 TDI 4Motion 16v,81,110,DFGA,199298127,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>VW6868,VOLKSWAGEN,Golf VII,2017,2020,Diesel,2.0 TDI 4Motion 16v,81,110,DFGA,199298205,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>VW6868,VOLKSWAGEN,Golf VII,2017,2020,Diesel,2.0 TDI 4Motion 16v,81,110,DFGA,199298255,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>VW6868,VOLKSWAGEN,Golf VII,2017,2020,Diesel,2.0 TDI 4Motion 16v,81,110,DFGA,199298361,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>VW6868,VOLKSWAGEN,Golf VII,2017,2020,Diesel,2.0 TDI 4Motion 16v,81,110,DFGA,199302283,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>VW6868,VOLKSWAGEN,Golf VII,2017,2020,Diesel,2.0 TDI 4Motion 16v,81,110,DFGA,199306455,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>VW6868,VOLKSWAGEN,Golf VII,2017,2020,Diesel,2.0 TDI 4Motion 16v,81,110,DFGA,199309415,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>VW6868,VOLKSWAGEN,Golf VII,2017,2020,Diesel,2.0 TDI 4Motion 16v,81,110,DFGA,199311279,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>VW6868,VOLKSWAGEN,Golf VII,2017,2020,Diesel,2.0 TDI 4Motion 16v,81,110,DFGA,199320371,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>VW6868,VOLKSWAGEN,Golf VII,2017,2020,Diesel,2.0 TDI 4Motion 16v,81,110,DFGA,199320408,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>VW6868,VOLKSWAGEN,Golf VII,2017,2020,Diesel,2.0 TDI 4Motion 16v,81,110,DFGA,199320445,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>VW6868,VOLKSWAGEN,Golf VII,2017,2020,Diesel,2.0 TDI 4Motion 16v,81,110,DFGA,25053801,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>VW6868,VOLKSWAGEN,Golf VII,2017,2020,Diesel,2.0 TDI 4Motion 16v,81,110,DFGA,25059645,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>VW6868,VOLKSWAGEN,Golf VII,2017,2020,Diesel,2.0 TDI 4Motion 16v,81,110,DFGA,62508157,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>VW6868,VOLKSWAGEN,Golf VII,2017,2020,Diesel,2.0 TDI 4Motion 16v,81,110,DFGA,62508877,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>BW2966,BMW,Serie 3,2018,9999,Diesel,320 d 16v,103,140,B47 D20B,00000154,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>BW2966,BMW,Serie 3,2018,9999,Diesel,320 d 16v,103,140,B47 D20B,00001440,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>BW2966,BMW,Serie 3,2018,9999,Diesel,320 d 16v,103,140,B47 D20B,15000123,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>BW2966,BMW,Serie 3,2018,9999,Diesel,320 d 16v,103,140,B47 D20B,15000158,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>BW2966,BMW,Serie 3,2018,9999,Diesel,320 d 16v,103,140,B47 D20B,15000159,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>BW2966,BMW,Serie 3,2018,9999,Diesel,320 d 16v,103,140,B47 D20B,199070454,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>BW2966,BMW,Serie 3,2018,9999,Diesel,320 d 16v,103,140,B47 D20B,199073831,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>BW2966,BMW,Serie 3,2018,9999,Diesel,320 d 16v,103,140,B47 D20B,199082245,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>BW2966,BMW,Serie 3,2018,9999,Diesel,320 d 16v,103,140,B47 D20B,199082246,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>BW2966,BMW,Serie 3,2018,9999,Diesel,320 d 16v,103,140,B47 D20B,199091060,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>BW2966,BMW,Serie 3,2018,9999,Diesel,320 d 16v,103,140,B47 D20B,199094802,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>BW2966,BMW,Serie 3,2018,9999,Diesel,320 d 16v,103,140,B47 D20B,199203407,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>BW2966,BMW,Serie 3,2018,9999,Diesel,320 d 16v,103,140,B47 D20B,199217638,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>BW2966,BMW,Serie 3,2018,9999,Diesel,320 d 16v,103,140,B47 D20B,199273876,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>BW2966,BMW,Serie 3,2018,9999,Diesel,320 d 16v,103,140,B47 D20B,199273878,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>BW2966,BMW,Serie 3,2018,9999,Diesel,320 d 16v,103,140,B47 D20B,199273879,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>BW2966,BMW,Serie 3,2018,9999,Diesel,320 d 16v,103,140,B47 D20B,199273881,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>BW2966,BMW,Serie 3,2018,9999,Diesel,320 d 16v,103,140,B47 D20B,199273885,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>BW2966,BMW,Serie 3,2018,9999,Diesel,320 d 16v,103,140,B47 D20B,199273887,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>BW2966,BMW,Serie 3,2018,9999,Diesel,320 d 16v,103,140,B47 D20B,199273892,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>BW2966,BMW,Serie 3,2018,9999,Diesel,320 d 16v,103,140,B47 D20B,199273899,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>BW2966,BMW,Serie 3,2018,9999,Diesel,320 d 16v,103,140,B47 D20B,199273900,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>BW2966,BMW,Serie 3,2018,9999,Diesel,320 d 16v,103,140,B47 D20B,199273901,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>BW2966,BMW,Serie 3,2018,9999,Diesel,320 d 16v,103,140,B47 D20B,199273902,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>BW2966,BMW,Serie 3,2018,9999,Diesel,320 d 16v,103,140,B47 D20B,199273903,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>BW2966,BMW,Serie 3,2018,9999,Diesel,320 d 16v,103,140,B47 D20B,199273905,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>BW2966,BMW,Serie 3,2018,9999,Diesel,320 d 16v,103,140,B47 D20B,199274467,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>BW2966,BMW,Serie 3,2018,9999,Diesel,320 d 16v,103,140,B47 D20B,199274536,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>BW2966,BMW,Serie 3,2018,9999,Diesel,320 d 16v,103,140,B47 D20B,199275734,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>BW2966,BMW,Serie 3,2018,9999,Diesel,320 d 16v,103,140,B47 D20B,199275862,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>BW2966,BMW,Serie 3,2018,9999,Diesel,320 d 16v,103,140,B47 D20B,199288327,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>BW2966,BMW,Serie 3,2018,9999,Diesel,320 d 16v,103,140,B47 D20B,199288337,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>BW2966,BMW,Serie 3,2018,9999,Diesel,320 d 16v,103,140,B47 D20B,199288604,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>BW2966,BMW,Serie 3,2018,9999,Diesel,320 d 16v,103,140,B47 D20B,199288609,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>BW2966,BMW,Serie 3,2018,9999,Diesel,320 d 16v,103,140,B47 D20B,199288948,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>BW2966,BMW,Serie 3,2018,9999,Diesel,320 d 16v,103,140,B47 D20B,199288964,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>BW2966,BMW,Serie 3,2018,9999,Diesel,320 d 16v,103,140,B47 D20B,199290180,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>BW2966,BMW,Serie 3,2018,9999,Diesel,320 d 16v,103,140,B47 D20B,199290550,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>BW2966,BMW,Serie 3,2018,9999,Diesel,320 d 16v,103,140,B47 D20B,199290569,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>BW2966,BMW,Serie 3,2018,9999,Diesel,320 d 16v,103,140,B47 D20B,199292558,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>BW2966,BMW,Serie 3,2018,9999,Diesel,320 d 16v,103,140,B47 D20B,199292582,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>BW2966,BMW,Serie 3,2018,9999,Diesel,320 d 16v,103,140,B47 D20B,199292597,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>BW2966,BMW,Serie 3,2018,9999,Diesel,320 d 16v,103,140,B47 D20B,199292615,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>BW2966,BMW,Serie 3,2018,9999,Diesel,320 d 16v,103,140,B47 D20B,199309024,,,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>BW2966,BMW,Serie 3,2018,9999,Diesel,320 d 16v,103,140,B47 D20B,75010014,,,,,</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
